--- a/docs/detailed-design-main.xlsx
+++ b/docs/detailed-design-main.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSCode\BetterCrewLink\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FCE533-4CD2-4075-8918-BE39B6CE4E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="5985" yWindow="-16170" windowWidth="26910" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -25,7 +31,7 @@
     <sheet name="図_距離_壁_カメラ" sheetId="16" r:id="rId16"/>
     <sheet name="図_ボイスエフェクト" sheetId="17" r:id="rId17"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -500,21 +506,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="28"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Meiryo"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -542,8 +541,30 @@
       <name val="Meiryo"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <color theme="0"/>
+      <name val="Meiryo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <color theme="0"/>
+      <name val="Meiryo"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -559,6 +580,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9ECFB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -590,30 +617,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -634,7 +670,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="symbols.png"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="symbols.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -677,7 +719,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="startup.png"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="startup.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -720,7 +768,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="gamestate.png"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="gamestate.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -763,7 +817,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="audio_conn.png"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="audio_conn.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -806,7 +866,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="overlay.png"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="overlay.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -844,12 +910,18 @@
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>236220</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="voice_hear.png"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="voice_hear.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0E00-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -863,7 +935,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="8503920" cy="4937760"/>
+          <a:ext cx="9723120" cy="6705600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -887,12 +959,18 @@
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>236220</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="distance_wall_camera.png"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="distance_wall_camera.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0F00-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -906,7 +984,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="8503920" cy="4937760"/>
+          <a:ext cx="9723120" cy="6896100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -930,12 +1008,18 @@
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>236220</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="voice_effect.png"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="voice_effect.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -949,7 +1033,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="8503920" cy="4663440"/>
+          <a:ext cx="9723120" cy="6667500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -962,9 +1046,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1002,7 +1086,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1036,6 +1120,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1070,9 +1155,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1245,270 +1331,269 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B3:E10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="42.7109375" customWidth="1"/>
-    <col min="4" max="4" width="66.7109375" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="1" max="1" width="24.75" customWidth="1"/>
+    <col min="2" max="2" width="42.75" customWidth="1"/>
+    <col min="3" max="3" width="66.75" customWidth="1"/>
+    <col min="4" max="4" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5">
-      <c r="B3" s="1" t="s">
+    <row r="1" spans="1:4" ht="42" customHeight="1">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="2:5">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="6" spans="2:5">
-      <c r="B6" s="2" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+    </row>
+    <row r="3" spans="1:4" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
-      <c r="B7" s="2" t="s">
+    <row r="4" spans="1:4" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:5">
-      <c r="B8" s="2" t="s">
+    <row r="5" spans="1:4" ht="18.75">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:5">
-      <c r="B10" s="2" t="s">
+    <row r="7" spans="1:4" ht="97.5">
+      <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="B7" s="7" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B3:E4"/>
-  </mergeCells>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="26" width="3.7109375" customWidth="1"/>
+    <col min="1" max="26" width="3.75" customWidth="1"/>
   </cols>
   <sheetData/>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="26" width="3.7109375" customWidth="1"/>
+    <col min="1" max="26" width="3.75" customWidth="1"/>
   </cols>
   <sheetData/>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="26" width="3.7109375" customWidth="1"/>
+    <col min="1" max="26" width="3.75" customWidth="1"/>
   </cols>
   <sheetData/>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="26" width="3.7109375" customWidth="1"/>
+    <col min="1" max="26" width="3.75" customWidth="1"/>
   </cols>
   <sheetData/>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="26" width="3.7109375" customWidth="1"/>
+    <col min="1" max="26" width="3.75" customWidth="1"/>
   </cols>
   <sheetData/>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="26" width="3.7109375" customWidth="1"/>
+    <col min="1" max="26" width="3.75" customWidth="1"/>
   </cols>
   <sheetData/>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="26" width="3.7109375" customWidth="1"/>
+    <col min="1" max="26" width="3.75" customWidth="1"/>
   </cols>
   <sheetData/>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="26" width="3.7109375" customWidth="1"/>
+    <col min="1" max="26" width="3.75" customWidth="1"/>
   </cols>
   <sheetData/>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="42.7109375" customWidth="1"/>
-    <col min="4" max="4" width="66.7109375" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="1" max="1" width="5.75" customWidth="1"/>
+    <col min="2" max="2" width="24.75" customWidth="1"/>
+    <col min="3" max="3" width="42.75" customWidth="1"/>
+    <col min="4" max="4" width="66.75" customWidth="1"/>
+    <col min="5" max="5" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="32" customHeight="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" ht="32.1" customHeight="1">
+      <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:5" ht="37.5">
+      <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:5" ht="37.5">
+      <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:5" ht="37.5">
+      <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:5" ht="37.5">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:5" ht="37.5">
+      <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:5" ht="37.5">
+      <c r="A9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1516,116 +1601,117 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="42.7109375" customWidth="1"/>
-    <col min="4" max="4" width="66.7109375" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="1" max="1" width="5.75" customWidth="1"/>
+    <col min="2" max="2" width="24.75" customWidth="1"/>
+    <col min="3" max="3" width="42.75" customWidth="1"/>
+    <col min="4" max="4" width="66.75" customWidth="1"/>
+    <col min="5" max="5" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="32" customHeight="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" ht="32.1" customHeight="1">
+      <c r="A1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3">
+    <row r="4" spans="1:5" ht="37.5">
+      <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3">
+    <row r="5" spans="1:5" ht="37.5">
+      <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3">
+    <row r="6" spans="1:5" ht="37.5">
+      <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3">
+    <row r="7" spans="1:5" ht="37.5">
+      <c r="A7" s="2">
         <v>4</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3">
+    <row r="8" spans="1:5" ht="37.5">
+      <c r="A8" s="2">
         <v>5</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="3">
+    <row r="9" spans="1:5" ht="18.75">
+      <c r="A9" s="2">
         <v>6</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="3">
+    <row r="10" spans="1:5" ht="18.75">
+      <c r="A10" s="2">
         <v>7</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1633,83 +1719,84 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="42.7109375" customWidth="1"/>
-    <col min="4" max="4" width="66.7109375" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="1" max="1" width="5.75" customWidth="1"/>
+    <col min="2" max="2" width="24.75" customWidth="1"/>
+    <col min="3" max="3" width="42.75" customWidth="1"/>
+    <col min="4" max="4" width="66.75" customWidth="1"/>
+    <col min="5" max="5" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="32" customHeight="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" ht="32.1" customHeight="1">
+      <c r="A1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:5" ht="93.75">
+      <c r="A4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:5" ht="93.75">
+      <c r="A5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:5" ht="131.25">
+      <c r="A6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:5" ht="93.75">
+      <c r="A7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1717,94 +1804,95 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="42.7109375" customWidth="1"/>
-    <col min="4" max="4" width="66.7109375" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="1" max="1" width="5.75" customWidth="1"/>
+    <col min="2" max="2" width="24.75" customWidth="1"/>
+    <col min="3" max="3" width="42.75" customWidth="1"/>
+    <col min="4" max="4" width="66.75" customWidth="1"/>
+    <col min="5" max="5" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="32" customHeight="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" ht="32.1" customHeight="1">
+      <c r="A1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:5" ht="75">
+      <c r="A4" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:5" ht="75">
+      <c r="A5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:5" ht="75">
+      <c r="A6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:5" ht="75">
+      <c r="A7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:5" ht="93.75">
+      <c r="A8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1812,94 +1900,95 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="42.7109375" customWidth="1"/>
-    <col min="4" max="4" width="66.7109375" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="1" max="1" width="5.75" customWidth="1"/>
+    <col min="2" max="2" width="24.75" customWidth="1"/>
+    <col min="3" max="3" width="42.75" customWidth="1"/>
+    <col min="4" max="4" width="66.75" customWidth="1"/>
+    <col min="5" max="5" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="32" customHeight="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" ht="32.1" customHeight="1">
+      <c r="A1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:5" ht="56.25">
+      <c r="A4" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:5" ht="37.5">
+      <c r="A5" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:5" ht="75">
+      <c r="A6" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:5" ht="75">
+      <c r="A7" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:5" ht="37.5">
+      <c r="A8" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1907,160 +1996,161 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="42.7109375" customWidth="1"/>
-    <col min="4" max="4" width="66.7109375" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="1" max="1" width="5.75" customWidth="1"/>
+    <col min="2" max="2" width="24.75" customWidth="1"/>
+    <col min="3" max="3" width="42.75" customWidth="1"/>
+    <col min="4" max="4" width="66.75" customWidth="1"/>
+    <col min="5" max="5" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="32" customHeight="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" ht="32.1" customHeight="1">
+      <c r="A1" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:5" ht="75">
+      <c r="A4" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:5" ht="18.75">
+      <c r="A5" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:5" ht="18.75">
+      <c r="A6" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:5" ht="37.5">
+      <c r="A7" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:5" ht="37.5">
+      <c r="A8" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:5" ht="37.5">
+      <c r="A9" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:5" ht="37.5">
+      <c r="A10" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:5" ht="56.25">
+      <c r="A11" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:5" ht="37.5">
+      <c r="A12" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:5" ht="37.5">
+      <c r="A13" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:5" ht="56.25">
+      <c r="A14" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2068,83 +2158,84 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="42.7109375" customWidth="1"/>
-    <col min="4" max="4" width="66.7109375" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="1" max="1" width="5.75" customWidth="1"/>
+    <col min="2" max="2" width="24.75" customWidth="1"/>
+    <col min="3" max="3" width="42.75" customWidth="1"/>
+    <col min="4" max="4" width="66.75" customWidth="1"/>
+    <col min="5" max="5" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="32" customHeight="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" ht="32.1" customHeight="1">
+      <c r="A1" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:5" ht="112.5">
+      <c r="A4" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:5" ht="93.75">
+      <c r="A5" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:5" ht="37.5">
+      <c r="A6" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:5" ht="75">
+      <c r="A7" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>135</v>
       </c>
     </row>
@@ -2152,94 +2243,95 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="42.7109375" customWidth="1"/>
-    <col min="4" max="4" width="66.7109375" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="1" max="1" width="5.75" customWidth="1"/>
+    <col min="2" max="2" width="24.75" customWidth="1"/>
+    <col min="3" max="3" width="42.75" customWidth="1"/>
+    <col min="4" max="4" width="66.75" customWidth="1"/>
+    <col min="5" max="5" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="32" customHeight="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" ht="32.1" customHeight="1">
+      <c r="A1" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:5" ht="56.25">
+      <c r="A4" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:5" ht="75">
+      <c r="A5" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:5" ht="37.5">
+      <c r="A6" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:5" ht="37.5">
+      <c r="A7" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:5" ht="37.5">
+      <c r="A8" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>154</v>
       </c>
     </row>
@@ -2247,6 +2339,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>